--- a/crates/xlstream-eval/tests/fixtures/financial/basic_financial.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/financial/basic_financial.xlsx
@@ -20,18 +20,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t xml:space="preserve">rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment</t>
+  </si>
   <si>
     <t xml:space="preserve">pmt</t>
   </si>
   <si>
-    <t xml:space="preserve">pv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rate</t>
+    <t xml:space="preserve">pv_calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fv_calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rate_calc</t>
   </si>
 </sst>
 </file>
@@ -314,7 +329,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -330,23 +345,284 @@
       <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <f aca="false">PMT(0.05/12,360,-200000)</f>
+      <c r="A2" s="0" t="n">
+        <v>0.00416666666666667</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <f aca="false">PMT(A2,B2,C2)</f>
         <v>1073.64324602428</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">PV(0.08/12,120,-500)</f>
+      <c r="G2" s="1" t="n">
+        <f aca="false">PV(A2,B2,E2)</f>
+        <v>-0</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <f aca="false">FV(A2,B2,E2)</f>
+        <v>-0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <f aca="false">RATE(B2,F2,C2)</f>
+        <v>0.00416666666668113</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>0.00666666666666667</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <f aca="false">PMT(A3,B3,C3)</f>
+        <v>-0</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <f aca="false">PV(A3,B3,E3)</f>
         <v>41210.7404466905</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <f aca="false">FV(0.06/12,240,-200)</f>
+      <c r="H3" s="1" t="n">
+        <f aca="false">FV(A3,B3,E3)</f>
+        <v>91473.0175908533</v>
+      </c>
+      <c r="I3" s="2" t="e">
+        <f aca="false">RATE(B3,E3,C3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <f aca="false">PMT(A4,B4,C4)</f>
+        <v>-0</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <f aca="false">PV(A4,B4,E4)</f>
+        <v>27916.1543365855</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <f aca="false">FV(A4,B4,E4)</f>
         <v>92408.1790322946</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <f aca="false">RATE(120,-500,50000)</f>
-        <v>0.00311418194602181</v>
+      <c r="I4" s="2" t="e">
+        <f aca="false">RATE(B4,E4,C4)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>0.00833333333333333</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <f aca="false">PMT(A5,B5,C5)</f>
+        <v>212.470447112683</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <f aca="false">PV(A5,B5,E5)</f>
+        <v>-0</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <f aca="false">FV(A5,B5,E5)</f>
+        <v>-0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <f aca="false">RATE(B5,F5,C5)</f>
+        <v>0.00833333333344944</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <f aca="false">PMT(A6,B6,C6)</f>
+        <v>100</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <f aca="false">PV(A6,B6,E6)</f>
+        <v>-0</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <f aca="false">FV(A6,B6,E6)</f>
+        <v>-0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <f aca="false">RATE(B6,F6,C6)</f>
+        <v>1.70466924136523E-010</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <f aca="false">PMT(A7,B7,C7)</f>
+        <v>1010</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <f aca="false">PV(A7,B7,E7)</f>
+        <v>-0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <f aca="false">FV(A7,B7,E7)</f>
+        <v>-0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <f aca="false">RATE(B7,F7,C7)</f>
+        <v>0.0100000000000055</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>0.00416666666666667</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <f aca="false">PMT(A8,B8,C8)</f>
+        <v>2684.1081150607</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <f aca="false">PV(A8,B8,E8)</f>
+        <v>-0</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <f aca="false">FV(A8,B8,E8)</f>
+        <v>-0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <f aca="false">RATE(B8,F8,C8)</f>
+        <v>0.00416666666668113</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <f aca="false">PMT(A9,B9,C9)</f>
+        <v>690.58164027799</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <f aca="false">PV(A9,B9,E9)</f>
+        <v>-0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <f aca="false">FV(A9,B9,E9)</f>
+        <v>-0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <f aca="false">RATE(B9,F9,C9)</f>
+        <v>0.00250000000000032</v>
       </c>
     </row>
   </sheetData>

--- a/crates/xlstream-eval/tests/fixtures/financial/basic_financial.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/financial/basic_financial.xlsx
@@ -325,7 +325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -424,7 +424,7 @@
       </c>
       <c r="I3" s="2" t="e">
         <f aca="false">RATE(B3,E3,C3)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -457,7 +457,7 @@
       </c>
       <c r="I4" s="2" t="e">
         <f aca="false">RATE(B4,E4,C4)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -520,10 +520,6 @@
       <c r="H6" s="1" t="n">
         <f aca="false">FV(A6,B6,E6)</f>
         <v>-0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <f aca="false">RATE(B6,F6,C6)</f>
-        <v>1.70466924136523E-010</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
